--- a/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/combined_data_visits_users.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/combined_data_visits_users.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,17 +367,32 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>mean_visits</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>n_exposed</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>sd_visits</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>se_visits</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ci_lower</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ci_upper</t>
         </is>
       </c>
     </row>
@@ -391,13 +406,22 @@
         <v>1</v>
       </c>
       <c r="C2">
+        <v>34155</v>
+      </c>
+      <c r="D2">
         <v>1.665122854914197</v>
       </c>
-      <c r="D2">
-        <v>34155</v>
-      </c>
       <c r="E2">
-        <v>5.978651296653447E-05</v>
+        <v>2.042008350371985</v>
+      </c>
+      <c r="F2">
+        <v>0.01104918814742904</v>
+      </c>
+      <c r="G2">
+        <v>1.64346607660471</v>
+      </c>
+      <c r="H2">
+        <v>1.686779633223683</v>
       </c>
     </row>
     <row r="3">
@@ -410,13 +434,22 @@
         <v>2</v>
       </c>
       <c r="C3">
+        <v>24352</v>
+      </c>
+      <c r="D3">
         <v>1.187207488299532</v>
       </c>
-      <c r="D3">
-        <v>24352</v>
-      </c>
       <c r="E3">
-        <v>7.687718984940927E-05</v>
+        <v>1.872113327212814</v>
+      </c>
+      <c r="F3">
+        <v>0.01199678338871503</v>
+      </c>
+      <c r="G3">
+        <v>1.16369305614515</v>
+      </c>
+      <c r="H3">
+        <v>1.210721920453914</v>
       </c>
     </row>
     <row r="4">
@@ -429,13 +462,22 @@
         <v>3</v>
       </c>
       <c r="C4">
+        <v>16561</v>
+      </c>
+      <c r="D4">
         <v>0.8073810452418096</v>
       </c>
-      <c r="D4">
-        <v>16561</v>
-      </c>
       <c r="E4">
-        <v>8.726589889752003E-05</v>
+        <v>1.445210551641829</v>
+      </c>
+      <c r="F4">
+        <v>0.0112302091648021</v>
+      </c>
+      <c r="G4">
+        <v>0.7853686308621499</v>
+      </c>
+      <c r="H4">
+        <v>0.8293934596214694</v>
       </c>
     </row>
     <row r="5">
@@ -448,13 +490,22 @@
         <v>4</v>
       </c>
       <c r="C5">
+        <v>11615</v>
+      </c>
+      <c r="D5">
         <v>0.5662539001560063</v>
       </c>
-      <c r="D5">
-        <v>11615</v>
-      </c>
       <c r="E5">
-        <v>0.0001081245340494253</v>
+        <v>1.255866462984074</v>
+      </c>
+      <c r="F5">
+        <v>0.01165289561175474</v>
+      </c>
+      <c r="G5">
+        <v>0.5434122639814706</v>
+      </c>
+      <c r="H5">
+        <v>0.589095536330542</v>
       </c>
     </row>
     <row r="6">
@@ -467,13 +518,22 @@
         <v>5</v>
       </c>
       <c r="C6">
+        <v>8863</v>
+      </c>
+      <c r="D6">
         <v>0.4320885335413416</v>
       </c>
-      <c r="D6">
-        <v>8863</v>
-      </c>
       <c r="E6">
-        <v>0.0001143487172280563</v>
+        <v>1.013472680792263</v>
+      </c>
+      <c r="F6">
+        <v>0.01076518931530118</v>
+      </c>
+      <c r="G6">
+        <v>0.4109862680731581</v>
+      </c>
+      <c r="H6">
+        <v>0.4531907990095251</v>
       </c>
     </row>
     <row r="7">
@@ -486,13 +546,22 @@
         <v>6</v>
       </c>
       <c r="C7">
+        <v>7101</v>
+      </c>
+      <c r="D7">
         <v>0.3461875975039002</v>
       </c>
-      <c r="D7">
-        <v>7101</v>
-      </c>
       <c r="E7">
-        <v>0.0001252185308904546</v>
+        <v>0.8891767878531182</v>
+      </c>
+      <c r="F7">
+        <v>0.01055184396571807</v>
+      </c>
+      <c r="G7">
+        <v>0.325502837159039</v>
+      </c>
+      <c r="H7">
+        <v>0.3668723578487613</v>
       </c>
     </row>
     <row r="8">
@@ -505,13 +574,22 @@
         <v>7</v>
       </c>
       <c r="C8">
+        <v>5961</v>
+      </c>
+      <c r="D8">
         <v>0.2906103744149766</v>
       </c>
-      <c r="D8">
-        <v>5961</v>
-      </c>
       <c r="E8">
-        <v>0.0001384807288664568</v>
+        <v>0.8254836247729488</v>
+      </c>
+      <c r="F8">
+        <v>0.0106917526171289</v>
+      </c>
+      <c r="G8">
+        <v>0.2696506678435176</v>
+      </c>
+      <c r="H8">
+        <v>0.3115700809864356</v>
       </c>
     </row>
     <row r="9">
@@ -524,13 +602,22 @@
         <v>8</v>
       </c>
       <c r="C9">
+        <v>5119</v>
+      </c>
+      <c r="D9">
         <v>0.249561232449298</v>
       </c>
-      <c r="D9">
-        <v>5119</v>
-      </c>
       <c r="E9">
-        <v>0.0001485563387487707</v>
+        <v>0.7604598980549573</v>
+      </c>
+      <c r="F9">
+        <v>0.0106287881821169</v>
+      </c>
+      <c r="G9">
+        <v>0.2287242626617605</v>
+      </c>
+      <c r="H9">
+        <v>0.2703982022368355</v>
       </c>
     </row>
     <row r="10">
@@ -543,13 +630,22 @@
         <v>9</v>
       </c>
       <c r="C10">
+        <v>4574</v>
+      </c>
+      <c r="D10">
         <v>0.2229914196567863</v>
       </c>
-      <c r="D10">
-        <v>4574</v>
-      </c>
       <c r="E10">
-        <v>0.0001492901147344622</v>
+        <v>0.6828529847954302</v>
+      </c>
+      <c r="F10">
+        <v>0.01009669254988384</v>
+      </c>
+      <c r="G10">
+        <v>0.2031970268131043</v>
+      </c>
+      <c r="H10">
+        <v>0.2427858125004682</v>
       </c>
     </row>
     <row r="11">
@@ -562,13 +658,22 @@
         <v>10</v>
       </c>
       <c r="C11">
+        <v>4364</v>
+      </c>
+      <c r="D11">
         <v>0.2127535101404056</v>
       </c>
-      <c r="D11">
-        <v>4364</v>
-      </c>
       <c r="E11">
-        <v>0.0001547260698108186</v>
+        <v>0.6752245686544123</v>
+      </c>
+      <c r="F11">
+        <v>0.01022129364354642</v>
+      </c>
+      <c r="G11">
+        <v>0.1927145836371125</v>
+      </c>
+      <c r="H11">
+        <v>0.2327924366436987</v>
       </c>
     </row>
     <row r="12">
@@ -581,13 +686,22 @@
         <v>11</v>
       </c>
       <c r="C12">
+        <v>4062</v>
+      </c>
+      <c r="D12">
         <v>0.1980304212168487</v>
       </c>
-      <c r="D12">
-        <v>4062</v>
-      </c>
       <c r="E12">
-        <v>0.0001794946992165101</v>
+        <v>0.729107468217464</v>
+      </c>
+      <c r="F12">
+        <v>0.01143988311584541</v>
+      </c>
+      <c r="G12">
+        <v>0.1756019776491176</v>
+      </c>
+      <c r="H12">
+        <v>0.2204588647845797</v>
       </c>
     </row>
     <row r="13">
@@ -600,13 +714,22 @@
         <v>12</v>
       </c>
       <c r="C13">
+        <v>4149</v>
+      </c>
+      <c r="D13">
         <v>0.202271840873635</v>
       </c>
-      <c r="D13">
-        <v>4149</v>
-      </c>
       <c r="E13">
-        <v>0.0001623626256164449</v>
+        <v>0.6736425336826299</v>
+      </c>
+      <c r="F13">
+        <v>0.01045822023556715</v>
+      </c>
+      <c r="G13">
+        <v>0.1817681230217016</v>
+      </c>
+      <c r="H13">
+        <v>0.2227755587255683</v>
       </c>
     </row>
     <row r="14">
@@ -619,13 +742,22 @@
         <v>13</v>
       </c>
       <c r="C14">
+        <v>3559</v>
+      </c>
+      <c r="D14">
         <v>0.1735081903276131</v>
       </c>
-      <c r="D14">
-        <v>3559</v>
-      </c>
       <c r="E14">
-        <v>0.0001650742784890945</v>
+        <v>0.5874993571426873</v>
+      </c>
+      <c r="F14">
+        <v>0.009847894825450561</v>
+      </c>
+      <c r="G14">
+        <v>0.154200102936039</v>
+      </c>
+      <c r="H14">
+        <v>0.1928162777191872</v>
       </c>
     </row>
     <row r="15">
@@ -638,13 +770,22 @@
         <v>14</v>
       </c>
       <c r="C15">
+        <v>3515</v>
+      </c>
+      <c r="D15">
         <v>0.171363104524181</v>
       </c>
-      <c r="D15">
-        <v>3515</v>
-      </c>
       <c r="E15">
-        <v>0.000167060048647576</v>
+        <v>0.5872160709962296</v>
+      </c>
+      <c r="F15">
+        <v>0.009904561847314022</v>
+      </c>
+      <c r="G15">
+        <v>0.1519438312716027</v>
+      </c>
+      <c r="H15">
+        <v>0.1907823777767593</v>
       </c>
     </row>
     <row r="16">
@@ -657,13 +798,22 @@
         <v>15</v>
       </c>
       <c r="C16">
+        <v>3335</v>
+      </c>
+      <c r="D16">
         <v>0.1625877535101404</v>
       </c>
-      <c r="D16">
-        <v>3335</v>
-      </c>
       <c r="E16">
-        <v>0.0001784275389106973</v>
+        <v>0.5950558422671756</v>
+      </c>
+      <c r="F16">
+        <v>0.01030409381994187</v>
+      </c>
+      <c r="G16">
+        <v>0.1423847663473284</v>
+      </c>
+      <c r="H16">
+        <v>0.1827907406729524</v>
       </c>
     </row>
     <row r="17">
@@ -676,13 +826,22 @@
         <v>16</v>
       </c>
       <c r="C17">
+        <v>3331</v>
+      </c>
+      <c r="D17">
         <v>0.1623927457098284</v>
       </c>
-      <c r="D17">
-        <v>3331</v>
-      </c>
       <c r="E17">
-        <v>0.0001920059716262048</v>
+        <v>0.6395718914868883</v>
+      </c>
+      <c r="F17">
+        <v>0.01108158934673856</v>
+      </c>
+      <c r="G17">
+        <v>0.14066533242222</v>
+      </c>
+      <c r="H17">
+        <v>0.1841201589974368</v>
       </c>
     </row>
     <row r="18">
@@ -695,13 +854,22 @@
         <v>17</v>
       </c>
       <c r="C18">
+        <v>3231</v>
+      </c>
+      <c r="D18">
         <v>0.1575175507020281</v>
       </c>
-      <c r="D18">
-        <v>3231</v>
-      </c>
       <c r="E18">
-        <v>0.0001873298463496039</v>
+        <v>0.6052627335555703</v>
+      </c>
+      <c r="F18">
+        <v>0.01064818176394948</v>
+      </c>
+      <c r="G18">
+        <v>0.1366396745126885</v>
+      </c>
+      <c r="H18">
+        <v>0.1783954268913677</v>
       </c>
     </row>
     <row r="19">
@@ -714,13 +882,22 @@
         <v>18</v>
       </c>
       <c r="C19">
+        <v>2994</v>
+      </c>
+      <c r="D19">
         <v>0.1459633385335413</v>
       </c>
-      <c r="D19">
-        <v>2994</v>
-      </c>
       <c r="E19">
-        <v>0.0001913064406175877</v>
+        <v>0.5727714832090575</v>
+      </c>
+      <c r="F19">
+        <v>0.01046780176254696</v>
+      </c>
+      <c r="G19">
+        <v>0.1254385239348224</v>
+      </c>
+      <c r="H19">
+        <v>0.1664881531322603</v>
       </c>
     </row>
     <row r="20">
@@ -733,13 +910,22 @@
         <v>19</v>
       </c>
       <c r="C20">
+        <v>2932</v>
+      </c>
+      <c r="D20">
         <v>0.1429407176287051</v>
       </c>
-      <c r="D20">
-        <v>2932</v>
-      </c>
       <c r="E20">
-        <v>0.000206801719105225</v>
+        <v>0.6063426404165198</v>
+      </c>
+      <c r="F20">
+        <v>0.01119788821184323</v>
+      </c>
+      <c r="G20">
+        <v>0.1209841930859482</v>
+      </c>
+      <c r="H20">
+        <v>0.1648972421714621</v>
       </c>
     </row>
     <row r="21">
@@ -752,13 +938,22 @@
         <v>20</v>
       </c>
       <c r="C21">
+        <v>2811</v>
+      </c>
+      <c r="D21">
         <v>0.1370417316692668</v>
       </c>
-      <c r="D21">
-        <v>2811</v>
-      </c>
       <c r="E21">
-        <v>0.0001957733712663814</v>
+        <v>0.550318946629798</v>
+      </c>
+      <c r="F21">
+        <v>0.01037968185704549</v>
+      </c>
+      <c r="G21">
+        <v>0.1166891625638619</v>
+      </c>
+      <c r="H21">
+        <v>0.1573943007746716</v>
       </c>
     </row>
     <row r="22">
@@ -771,13 +966,22 @@
         <v>21</v>
       </c>
       <c r="C22">
+        <v>2769</v>
+      </c>
+      <c r="D22">
         <v>0.1349941497659906</v>
       </c>
-      <c r="D22">
-        <v>2769</v>
-      </c>
       <c r="E22">
-        <v>0.0002102391328110141</v>
+        <v>0.5821521587536982</v>
+      </c>
+      <c r="F22">
+        <v>0.01106305405484568</v>
+      </c>
+      <c r="G22">
+        <v>0.1133014767647417</v>
+      </c>
+      <c r="H22">
+        <v>0.1566868227672396</v>
       </c>
     </row>
     <row r="23">
@@ -790,13 +994,22 @@
         <v>22</v>
       </c>
       <c r="C23">
+        <v>2515</v>
+      </c>
+      <c r="D23">
         <v>0.1226111544461778</v>
       </c>
-      <c r="D23">
-        <v>2515</v>
-      </c>
       <c r="E23">
-        <v>0.0002130833786520759</v>
+        <v>0.5359046973099708</v>
+      </c>
+      <c r="F23">
+        <v>0.01068608363893558</v>
+      </c>
+      <c r="G23">
+        <v>0.1016567269570389</v>
+      </c>
+      <c r="H23">
+        <v>0.1435655819353168</v>
       </c>
     </row>
     <row r="24">
@@ -809,13 +1022,22 @@
         <v>23</v>
       </c>
       <c r="C24">
+        <v>2496</v>
+      </c>
+      <c r="D24">
         <v>0.1216848673946958</v>
       </c>
-      <c r="D24">
-        <v>2496</v>
-      </c>
       <c r="E24">
-        <v>0.000225854280994888</v>
+        <v>0.5637322853632405</v>
+      </c>
+      <c r="F24">
+        <v>0.01128367626194228</v>
+      </c>
+      <c r="G24">
+        <v>0.09955853455657798</v>
+      </c>
+      <c r="H24">
+        <v>0.1438112002328136</v>
       </c>
     </row>
     <row r="25">
@@ -828,13 +1050,22 @@
         <v>24</v>
       </c>
       <c r="C25">
+        <v>2296</v>
+      </c>
+      <c r="D25">
         <v>0.1119344773790952</v>
       </c>
-      <c r="D25">
-        <v>2296</v>
-      </c>
       <c r="E25">
-        <v>0.0002219189768338523</v>
+        <v>0.509525970810525</v>
+      </c>
+      <c r="F25">
+        <v>0.01063360155885799</v>
+      </c>
+      <c r="G25">
+        <v>0.09108200396884519</v>
+      </c>
+      <c r="H25">
+        <v>0.1327869507893451</v>
       </c>
     </row>
     <row r="26">
@@ -847,13 +1078,22 @@
         <v>1</v>
       </c>
       <c r="C26">
+        <v>34533</v>
+      </c>
+      <c r="D26">
         <v>1.668986515876468</v>
       </c>
-      <c r="D26">
-        <v>34533</v>
-      </c>
       <c r="E26">
-        <v>5.936151499897333E-05</v>
+        <v>2.049931197459546</v>
+      </c>
+      <c r="F26">
+        <v>0.01103118404908821</v>
+      </c>
+      <c r="G26">
+        <v>1.647365034589619</v>
+      </c>
+      <c r="H26">
+        <v>1.690607997163317</v>
       </c>
     </row>
     <row r="27">
@@ -866,13 +1106,22 @@
         <v>2</v>
       </c>
       <c r="C27">
+        <v>24577</v>
+      </c>
+      <c r="D27">
         <v>1.187811125610169</v>
       </c>
-      <c r="D27">
-        <v>24577</v>
-      </c>
       <c r="E27">
-        <v>7.5464009217965E-05</v>
+        <v>1.854678954549926</v>
+      </c>
+      <c r="F27">
+        <v>0.01183053294330062</v>
+      </c>
+      <c r="G27">
+        <v>1.164622565090845</v>
+      </c>
+      <c r="H27">
+        <v>1.210999686129492</v>
       </c>
     </row>
     <row r="28">
@@ -885,13 +1134,22 @@
         <v>3</v>
       </c>
       <c r="C28">
+        <v>16721</v>
+      </c>
+      <c r="D28">
         <v>0.808129138272679</v>
       </c>
-      <c r="D28">
-        <v>16721</v>
-      </c>
       <c r="E28">
-        <v>8.486710940082252E-05</v>
+        <v>1.419062936291153</v>
+      </c>
+      <c r="F28">
+        <v>0.01097414094409552</v>
+      </c>
+      <c r="G28">
+        <v>0.7866186601143657</v>
+      </c>
+      <c r="H28">
+        <v>0.8296396164309923</v>
       </c>
     </row>
     <row r="29">
@@ -904,13 +1162,22 @@
         <v>4</v>
       </c>
       <c r="C29">
+        <v>11702</v>
+      </c>
+      <c r="D29">
         <v>0.565559905272824</v>
       </c>
-      <c r="D29">
-        <v>11702</v>
-      </c>
       <c r="E29">
-        <v>0.0001062722419657549</v>
+        <v>1.243597775483264</v>
+      </c>
+      <c r="F29">
+        <v>0.01149608297222284</v>
+      </c>
+      <c r="G29">
+        <v>0.5430256657208021</v>
+      </c>
+      <c r="H29">
+        <v>0.5880941448248458</v>
       </c>
     </row>
     <row r="30">
@@ -923,13 +1190,22 @@
         <v>5</v>
       </c>
       <c r="C30">
+        <v>8950</v>
+      </c>
+      <c r="D30">
         <v>0.4325552172442125</v>
       </c>
-      <c r="D30">
-        <v>8950</v>
-      </c>
       <c r="E30">
-        <v>0.0001131875406135622</v>
+        <v>1.013028488491381</v>
+      </c>
+      <c r="F30">
+        <v>0.01070804385421603</v>
+      </c>
+      <c r="G30">
+        <v>0.4115649979952459</v>
+      </c>
+      <c r="H30">
+        <v>0.453545436493179</v>
       </c>
     </row>
     <row r="31">
@@ -942,13 +1218,22 @@
         <v>6</v>
       </c>
       <c r="C31">
+        <v>7129</v>
+      </c>
+      <c r="D31">
         <v>0.3445459378473733</v>
       </c>
-      <c r="D31">
-        <v>7129</v>
-      </c>
       <c r="E31">
-        <v>0.0001241860489150962</v>
+        <v>0.8853223427157206</v>
+      </c>
+      <c r="F31">
+        <v>0.01048545105172505</v>
+      </c>
+      <c r="G31">
+        <v>0.3239913411765295</v>
+      </c>
+      <c r="H31">
+        <v>0.365100534518217</v>
       </c>
     </row>
     <row r="32">
@@ -961,13 +1246,22 @@
         <v>7</v>
       </c>
       <c r="C32">
+        <v>5973</v>
+      </c>
+      <c r="D32">
         <v>0.2886762360446571</v>
       </c>
-      <c r="D32">
-        <v>5973</v>
-      </c>
       <c r="E32">
-        <v>0.0001374658052325496</v>
+        <v>0.821083254654019</v>
+      </c>
+      <c r="F32">
+        <v>0.01062407034822235</v>
+      </c>
+      <c r="G32">
+        <v>0.267849219728225</v>
+      </c>
+      <c r="H32">
+        <v>0.3095032523610892</v>
       </c>
     </row>
     <row r="33">
@@ -980,13 +1274,22 @@
         <v>8</v>
       </c>
       <c r="C33">
+        <v>5155</v>
+      </c>
+      <c r="D33">
         <v>0.2491421390942922</v>
       </c>
-      <c r="D33">
-        <v>5155</v>
-      </c>
       <c r="E33">
-        <v>0.0001470970062614054</v>
+        <v>0.7582850672775446</v>
+      </c>
+      <c r="F33">
+        <v>0.01056131920212883</v>
+      </c>
+      <c r="G33">
+        <v>0.2284374715668712</v>
+      </c>
+      <c r="H33">
+        <v>0.2698468066217132</v>
       </c>
     </row>
     <row r="34">
@@ -999,13 +1302,22 @@
         <v>9</v>
       </c>
       <c r="C34">
+        <v>4593</v>
+      </c>
+      <c r="D34">
         <v>0.2219805712628679</v>
       </c>
-      <c r="D34">
-        <v>4593</v>
-      </c>
       <c r="E34">
-        <v>0.0001481162650835243</v>
+        <v>0.6802980055286268</v>
+      </c>
+      <c r="F34">
+        <v>0.01003808745342811</v>
+      </c>
+      <c r="G34">
+        <v>0.2023010942643581</v>
+      </c>
+      <c r="H34">
+        <v>0.2416600482613777</v>
       </c>
     </row>
     <row r="35">
@@ -1018,13 +1330,22 @@
         <v>10</v>
       </c>
       <c r="C35">
+        <v>4379</v>
+      </c>
+      <c r="D35">
         <v>0.2116379102025035</v>
       </c>
-      <c r="D35">
-        <v>4379</v>
-      </c>
       <c r="E35">
-        <v>0.00015328684769938</v>
+        <v>0.6712431060755849</v>
+      </c>
+      <c r="F35">
+        <v>0.01014360585641353</v>
+      </c>
+      <c r="G35">
+        <v>0.1917513101233627</v>
+      </c>
+      <c r="H35">
+        <v>0.2315245102816443</v>
       </c>
     </row>
     <row r="36">
@@ -1037,13 +1358,22 @@
         <v>11</v>
       </c>
       <c r="C36">
+        <v>4073</v>
+      </c>
+      <c r="D36">
         <v>0.1968488714900198</v>
       </c>
-      <c r="D36">
-        <v>4073</v>
-      </c>
       <c r="E36">
-        <v>0.0001775594330884355</v>
+        <v>0.7231995709691976</v>
+      </c>
+      <c r="F36">
+        <v>0.01133185359202503</v>
+      </c>
+      <c r="G36">
+        <v>0.1746322429157102</v>
+      </c>
+      <c r="H36">
+        <v>0.2190655000643294</v>
       </c>
     </row>
     <row r="37">
@@ -1056,13 +1386,22 @@
         <v>12</v>
       </c>
       <c r="C37">
+        <v>4180</v>
+      </c>
+      <c r="D37">
         <v>0.202020202020202</v>
       </c>
-      <c r="D37">
-        <v>4180</v>
-      </c>
       <c r="E37">
-        <v>0.0001610773970427804</v>
+        <v>0.6733035196388222</v>
+      </c>
+      <c r="F37">
+        <v>0.01041412398443403</v>
+      </c>
+      <c r="G37">
+        <v>0.1816029806650185</v>
+      </c>
+      <c r="H37">
+        <v>0.2224374233753856</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1414,22 @@
         <v>13</v>
       </c>
       <c r="C38">
+        <v>3556</v>
+      </c>
+      <c r="D38">
         <v>0.1718621622927843</v>
       </c>
-      <c r="D38">
-        <v>3556</v>
-      </c>
       <c r="E38">
-        <v>0.000163441039328151</v>
+        <v>0.5811963358509051</v>
+      </c>
+      <c r="F38">
+        <v>0.009746349736449287</v>
+      </c>
+      <c r="G38">
+        <v>0.1527531618580965</v>
+      </c>
+      <c r="H38">
+        <v>0.1909711627274721</v>
       </c>
     </row>
     <row r="39">
@@ -1094,13 +1442,22 @@
         <v>14</v>
       </c>
       <c r="C39">
+        <v>3533</v>
+      </c>
+      <c r="D39">
         <v>0.1707505678797545</v>
       </c>
-      <c r="D39">
-        <v>3533</v>
-      </c>
       <c r="E39">
-        <v>0.0001658982596418771</v>
+        <v>0.5861185513147519</v>
+      </c>
+      <c r="F39">
+        <v>0.009860834021873382</v>
+      </c>
+      <c r="G39">
+        <v>0.1514170630690026</v>
+      </c>
+      <c r="H39">
+        <v>0.1900840726905063</v>
       </c>
     </row>
     <row r="40">
@@ -1113,13 +1470,22 @@
         <v>15</v>
       </c>
       <c r="C40">
+        <v>3356</v>
+      </c>
+      <c r="D40">
         <v>0.162196123918612</v>
       </c>
-      <c r="D40">
-        <v>3356</v>
-      </c>
       <c r="E40">
-        <v>0.0001779816013308837</v>
+        <v>0.5973062540664457</v>
+      </c>
+      <c r="F40">
+        <v>0.01031065097768796</v>
+      </c>
+      <c r="G40">
+        <v>0.1419803262491514</v>
+      </c>
+      <c r="H40">
+        <v>0.1824119215880726</v>
       </c>
     </row>
     <row r="41">
@@ -1132,13 +1498,22 @@
         <v>16</v>
       </c>
       <c r="C41">
+        <v>3352</v>
+      </c>
+      <c r="D41">
         <v>0.1620028031511285</v>
       </c>
-      <c r="D41">
-        <v>3352</v>
-      </c>
       <c r="E41">
-        <v>0.0001894872891268274</v>
+        <v>0.6351613931531256</v>
+      </c>
+      <c r="F41">
+        <v>0.01097064312365528</v>
+      </c>
+      <c r="G41">
+        <v>0.1404929685430826</v>
+      </c>
+      <c r="H41">
+        <v>0.1835126377591744</v>
       </c>
     </row>
     <row r="42">
@@ -1151,13 +1526,22 @@
         <v>17</v>
       </c>
       <c r="C42">
+        <v>3270</v>
+      </c>
+      <c r="D42">
         <v>0.1580397274177179</v>
       </c>
-      <c r="D42">
-        <v>3270</v>
-      </c>
       <c r="E42">
-        <v>0.0001850660120328433</v>
+        <v>0.6051658593473977</v>
+      </c>
+      <c r="F42">
+        <v>0.01058279888346422</v>
+      </c>
+      <c r="G42">
+        <v>0.1372901401536206</v>
+      </c>
+      <c r="H42">
+        <v>0.1787893146818151</v>
       </c>
     </row>
     <row r="43">
@@ -1170,13 +1554,22 @@
         <v>18</v>
       </c>
       <c r="C43">
+        <v>3010</v>
+      </c>
+      <c r="D43">
         <v>0.1454738775312938</v>
       </c>
-      <c r="D43">
-        <v>3010</v>
-      </c>
       <c r="E43">
-        <v>0.000189818161182895</v>
+        <v>0.5713526651605141</v>
+      </c>
+      <c r="F43">
+        <v>0.01041408240257946</v>
+      </c>
+      <c r="G43">
+        <v>0.125054437464543</v>
+      </c>
+      <c r="H43">
+        <v>0.1658933175980446</v>
       </c>
     </row>
     <row r="44">
@@ -1189,13 +1582,22 @@
         <v>19</v>
       </c>
       <c r="C44">
+        <v>2943</v>
+      </c>
+      <c r="D44">
         <v>0.1422357546759461</v>
       </c>
-      <c r="D44">
-        <v>2943</v>
-      </c>
       <c r="E44">
-        <v>0.0002055636265817808</v>
+        <v>0.604973753030181</v>
+      </c>
+      <c r="F44">
+        <v>0.01115170832920565</v>
+      </c>
+      <c r="G44">
+        <v>0.1203698122066105</v>
+      </c>
+      <c r="H44">
+        <v>0.1641016971452817</v>
       </c>
     </row>
     <row r="45">
@@ -1208,13 +1610,22 @@
         <v>20</v>
       </c>
       <c r="C45">
+        <v>2830</v>
+      </c>
+      <c r="D45">
         <v>0.1367744429945387</v>
       </c>
-      <c r="D45">
-        <v>2830</v>
-      </c>
       <c r="E45">
-        <v>0.0001945666860378603</v>
+        <v>0.5506237214871447</v>
+      </c>
+      <c r="F45">
+        <v>0.01035050881568571</v>
+      </c>
+      <c r="G45">
+        <v>0.1164791353748972</v>
+      </c>
+      <c r="H45">
+        <v>0.1570697506141802</v>
       </c>
     </row>
     <row r="46">
@@ -1227,13 +1638,22 @@
         <v>21</v>
       </c>
       <c r="C46">
+        <v>2797</v>
+      </c>
+      <c r="D46">
         <v>0.1351795466628002</v>
       </c>
-      <c r="D46">
-        <v>2797</v>
-      </c>
       <c r="E46">
-        <v>0.0002079717338547552</v>
+        <v>0.5816969395917503</v>
+      </c>
+      <c r="F46">
+        <v>0.0109989327257194</v>
+      </c>
+      <c r="G46">
+        <v>0.1136126986153735</v>
+      </c>
+      <c r="H46">
+        <v>0.156746394710227</v>
       </c>
     </row>
     <row r="47">
@@ -1246,13 +1666,22 @@
         <v>22</v>
       </c>
       <c r="C47">
+        <v>2500</v>
+      </c>
+      <c r="D47">
         <v>0.1208254796771543</v>
       </c>
-      <c r="D47">
-        <v>2500</v>
-      </c>
       <c r="E47">
-        <v>0.0002110515695594124</v>
+        <v>0.5276289238985309</v>
+      </c>
+      <c r="F47">
+        <v>0.01055257847797062</v>
+      </c>
+      <c r="G47">
+        <v>0.1001327837069071</v>
+      </c>
+      <c r="H47">
+        <v>0.1415181756474015</v>
       </c>
     </row>
     <row r="48">
@@ -1265,13 +1694,22 @@
         <v>23</v>
       </c>
       <c r="C48">
+        <v>2499</v>
+      </c>
+      <c r="D48">
         <v>0.1207771494852835</v>
       </c>
-      <c r="D48">
-        <v>2499</v>
-      </c>
       <c r="E48">
-        <v>0.0002228913448268299</v>
+        <v>0.557005470722248</v>
+      </c>
+      <c r="F48">
+        <v>0.01114233810495729</v>
+      </c>
+      <c r="G48">
+        <v>0.09892798152976391</v>
+      </c>
+      <c r="H48">
+        <v>0.142626317440803</v>
       </c>
     </row>
     <row r="49">
@@ -1284,13 +1722,22 @@
         <v>24</v>
       </c>
       <c r="C49">
+        <v>2295</v>
+      </c>
+      <c r="D49">
         <v>0.1109177903436277</v>
       </c>
-      <c r="D49">
-        <v>2295</v>
-      </c>
       <c r="E49">
-        <v>0.0002200430813321485</v>
+        <v>0.5049988716572809</v>
+      </c>
+      <c r="F49">
+        <v>0.01054141868007937</v>
+      </c>
+      <c r="G49">
+        <v>0.09024608263695288</v>
+      </c>
+      <c r="H49">
+        <v>0.1315894980503025</v>
       </c>
     </row>
   </sheetData>
